--- a/proyecto_y_split/resultados_split.xlsx
+++ b/proyecto_y_split/resultados_split.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -492,8 +492,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -586,147 +585,154 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>x9</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+        <v>1.744762</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MATRIZ IM 7x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>x4</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>x6</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>x9</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>1.744762</v>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>MATRIZ IM 8x8</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>x2</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>x3</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>x4</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>x5</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>x6</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>x9</t>
-        </is>
+      <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.002443</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.002232</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.414958</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.006396</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.006914</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>x1</t>
+          <t>x2</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0</v>
+        <v>0.002443</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.002443</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.002232</v>
+        <v>0.000753</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3e-05</v>
+        <v>0.001334</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.414958</v>
+        <v>0.655467</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.006396</v>
+        <v>0.003924</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0.006914</v>
+        <v>0.005365</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>x2</t>
+          <t>x3</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.002443</v>
+        <v>0.002232</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0</v>
+        <v>0.000753</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.000753</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.001334</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>0.655467</v>
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.000722</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.003924</v>
+        <v>0.000106</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0.005365</v>
+        <v>0.000107</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>x3</t>
+          <t>x4</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.002232</v>
+        <v>3e-05</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.000753</v>
+        <v>0.001334</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>0</v>
@@ -735,650 +741,499 @@
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.000722</v>
+        <v>0.00629</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.000106</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>0.000107</v>
+        <v>0.000116</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.747456</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>x4</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>0.001334</v>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>0.414958</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.655467</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0</v>
+        <v>0.000722</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>0.00629</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.00629</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.000116</v>
+        <v>0.009532000000000001</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0.747456</v>
+        <v>0.016187</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>x5</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>0.414958</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>0.655467</v>
+          <t>x6</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>0.006396</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>0.003924</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.000722</v>
+        <v>0.000106</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.00629</v>
+        <v>0.000116</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0</v>
+        <v>0.009532000000000001</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.009532000000000001</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0.016187</v>
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.997422</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>x9</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0.006914</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0.005365</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.000107</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.747456</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.016187</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.997422</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>MATRIZ DE DISTANCIAS 7x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>x4</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
           <t>x6</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>0.006396</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>0.003924</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>0.000106</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0.000116</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.009532000000000001</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0.997422</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>x9</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0.006914</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>0.005365</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>0.000107</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0.747456</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>0.016187</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0.997422</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24"/>
+    </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>MATRIZ DE DISTANCIAS 8x8</t>
-        </is>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0.996779</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0.996689</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0.999959</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.452969</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0.991569</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0.990885</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>x1</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>x3</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>x4</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>x5</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>x6</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>x9</t>
-        </is>
+      <c r="B26" s="4" t="n">
+        <v>0.996779</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0.998883</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.998216</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.343925</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.996065</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.99463</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>x1</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>0</v>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>0.996689</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.996779</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>0.996689</v>
+        <v>0.998883</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.999959</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>0.452969</v>
+        <v>1</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.99893</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.991569</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>0.990885</v>
+        <v>0.999843</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0.999841</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>x2</t>
+          <t>x4</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>0.996779</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>0</v>
+        <v>0.999959</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0.998216</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.998883</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>0.998216</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>0.343925</v>
+        <v>1</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0.991585</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.996065</v>
+        <v>0.999844</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>0.99463</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>x3</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>0.996689</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>0.998883</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>0</v>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>0.452969</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0.343925</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0.99893</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0.99893</v>
+        <v>0.991585</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.999843</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>0.999841</v>
+        <v>0.990443</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0.988533</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>x4</t>
+          <t>x6</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>0.999959</v>
+        <v>0.991569</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.998216</v>
+        <v>0.996065</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>0</v>
+        <v>0.999843</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0.999844</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.991585</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>0.999844</v>
+        <v>0.990443</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>x5</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>0.452969</v>
-      </c>
-      <c r="C31" s="6" t="n">
+          <t>x9</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>0.990885</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0.99463</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0.999841</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0.988533</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>MST MIN (distancias) - Costo: 2.782115</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Arista</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Distancia d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>x9 -- x4</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>x9 -- x6</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>x5 -- x2</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
         <v>0.343925</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>0.99893</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>0.991585</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>0.990443</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>0.988533</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>x6</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>0.991569</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>0.996065</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>0.999843</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0.999844</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>0.990443</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>x9</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>0.990885</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>0.99463</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>0.999841</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>0.988533</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>MST MIN (distancias) - Costo: 0.000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Arista</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Distancia d</t>
-        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>x1 -- Y</t>
+          <t>x1 -- x5</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0</v>
+        <v>0.452969</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Y -- x2</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n">
-        <v>0</v>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>x5 -- x9</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>0.988533</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Y -- x3</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Y -- x4</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>x1 -- x3</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>0.996689</v>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>x4 -- x9</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n">
-        <v>0</v>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>MST MAX (MI directa) - Costo: 2.833722</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Y -- x5</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>0</v>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Arista</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Peso MI</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Y -- x6</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45"/>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>x9 -- x6</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>0.997422</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>x9 -- x4</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>0.747456</v>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>MST MAX (MI directa) - Costo: 2.833722</t>
-        </is>
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>x5 -- x2</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>0.655467</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Arista</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Peso MI</t>
-        </is>
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>x1 -- x5</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>0.414958</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>x9 -- x6</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>0.997422</v>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>x5 -- x9</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>0.016187</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>x9 -- x4</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>0.747456</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>x5 -- x2</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="n">
-        <v>0.655467</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>x1 -- x5</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="n">
-        <v>0.414958</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>x5 -- x9</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>0.016187</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>x1 -- x3</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B49" s="4" t="n">
         <v>0.002232</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>x1 -- Y</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1395,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1405,8 +1260,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1499,799 +1353,655 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>x9</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+        <v>1.685441</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MATRIZ IM 7x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>x4</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>x6</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>x9</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>1.685441</v>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>MATRIZ IM 8x8</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>x2</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>x3</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>x4</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>x5</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>x6</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>x9</t>
-        </is>
+      <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.006098</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.000546</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.00181</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.423706</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.000384</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.002923</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>x1</t>
+          <t>x2</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0</v>
+        <v>0.006098</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.006098</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.000546</v>
+        <v>0.000556</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.00181</v>
+        <v>2e-05</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.423706</v>
+        <v>0.686923</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.000384</v>
+        <v>0.00017</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0.002923</v>
+        <v>0.00314</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>x2</t>
+          <t>x3</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.006098</v>
+        <v>0.000546</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.000556</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2e-05</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>0.686923</v>
+        <v>0.004818</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.001206</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.00017</v>
+        <v>0.000384</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0.00314</v>
+        <v>0.005813</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>x3</t>
+          <t>x4</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.000546</v>
+        <v>0.00181</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.000556</v>
+        <v>2e-05</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0</v>
+        <v>0.004818</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.004818</v>
+        <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.001206</v>
+        <v>0.001194</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.000384</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>0.005813</v>
+        <v>0.000388</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.686015</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>x4</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>0.00181</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>2e-05</v>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>0.423706</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.686923</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.004818</v>
+        <v>0.001206</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>0.001194</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.001194</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.000388</v>
+        <v>0.000761</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0.686015</v>
+        <v>0.006917</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>x5</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>0.423706</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>0.686923</v>
+          <t>x6</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>0.000384</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>0.00017</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.001206</v>
+        <v>0.000384</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.001194</v>
+        <v>0.000388</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0</v>
+        <v>0.000761</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.000761</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0.006917</v>
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.999814</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>x9</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0.002923</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0.00314</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.005813</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.686015</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.006917</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.999814</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>MATRIZ DE DISTANCIAS 7x7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>x4</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
           <t>x6</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>0.000384</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>0.00017</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>0.000384</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0.000388</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.000761</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0.999814</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>x9</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0.002923</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>0.00314</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>0.005813</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0.686015</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>0.006917</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0.999814</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24"/>
+    </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>MATRIZ DE DISTANCIAS 8x8</t>
-        </is>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0.991708</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0.999258</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0.997362</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.423823</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0.999478</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0.996025</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>x1</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>x2</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>x3</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>x4</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>x5</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>x6</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>x9</t>
-        </is>
+      <c r="B26" s="4" t="n">
+        <v>0.991708</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0.999251</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.99997</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.312108</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.999829</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0.996855</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>x1</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>0</v>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>0.999258</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.991708</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>0.999258</v>
+        <v>0.999251</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.997362</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>0.423823</v>
+        <v>0.992976</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.998377</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.999478</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>0.996025</v>
+        <v>0.999483</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0.992178</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>x2</t>
+          <t>x4</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>0.991708</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>0</v>
+        <v>0.997362</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0.99997</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.999251</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>0.99997</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>0.312108</v>
+        <v>0.992976</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0.99826</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.999829</v>
+        <v>0.999435</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>0.996855</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>x3</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>0.999258</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>0.999251</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>0</v>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>0.423823</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0.312108</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0.998377</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.992976</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0.998377</v>
+        <v>0.99826</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.999483</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>0.992178</v>
+        <v>0.999239</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0.995116</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>x4</t>
+          <t>x6</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>0.997362</v>
+        <v>0.999478</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.99997</v>
+        <v>0.999829</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.992976</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>0</v>
+        <v>0.999483</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0.999435</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.99826</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>0.999435</v>
+        <v>0.999239</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>x5</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>0.423823</v>
-      </c>
-      <c r="C31" s="6" t="n">
+          <t>x9</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>0.996025</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0.996855</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0.992178</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0.995116</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>MST MIN (distancias) - Costo: 2.723224</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Arista</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Distancia d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>x9 -- x6</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>x9 -- x4</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>x5 -- x2</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
         <v>0.312108</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>0.998377</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>0.99826</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>0.999239</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>0.995116</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>x6</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>0.999478</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>0.999829</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>0.999483</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>0.999435</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>0.999239</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>x9</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>0.996025</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>0.996855</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>0.992178</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>0.995116</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>MST MIN (distancias) - Costo: 0.000000</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Arista</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Distancia d</t>
-        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>x1 -- Y</t>
+          <t>x1 -- x5</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0</v>
+        <v>0.423823</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Y -- x2</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n">
-        <v>0</v>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>x9 -- x3</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>0.992178</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Y -- x3</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Y -- x4</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>x5 -- x9</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>0.995116</v>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Y -- x5</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n">
-        <v>0</v>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>MST MAX (MI directa) - Costo: 2.809188</t>
+        </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Y -- x6</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>0</v>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Arista</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Peso MI</t>
+        </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>x6 -- x9</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45"/>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>x9 -- x6</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>0.999814</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>x5 -- x2</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>0.686923</v>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>MST MAX (MI directa) - Costo: 2.809188</t>
-        </is>
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>x9 -- x4</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>0.686015</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Arista</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Peso MI</t>
-        </is>
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>x1 -- x5</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>0.423706</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>x9 -- x6</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>0.999814</v>
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>x5 -- x9</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>0.006917</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>x5 -- x2</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>0.686923</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>x9 -- x4</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="n">
-        <v>0.686015</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>x1 -- x5</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="n">
-        <v>0.423706</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>x5 -- x9</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>0.006917</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>x9 -- x3</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B49" s="4" t="n">
         <v>0.005813</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>x1 -- Y</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2383,10 +2093,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>2.782115</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>2.723224</v>
       </c>
     </row>
     <row r="7">
@@ -2396,10 +2106,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>2.782115</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0</v>
+        <v>2.723224</v>
       </c>
     </row>
     <row r="8">
